--- a/upload/mp-2025.xlsx
+++ b/upload/mp-2025.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R9781039b071c453c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R460c00e21afe4123"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1555,6 +1555,22 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>CHPB</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>29.113636363636363</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>CSPD</x:t>
         </x:is>
       </x:c>
@@ -4099,6 +4115,22 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>CSSFA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>77.875</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>CSSFE</x:t>
         </x:is>
       </x:c>
@@ -6755,6 +6787,22 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>CSSI</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>25.127272727272729</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>HAC</x:t>
         </x:is>
       </x:c>
@@ -8157,7 +8205,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>7.2710280373831777</x:v>
+        <x:v>7.2484472049689437</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -8221,7 +8269,23 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>6.2758620689655169</x:v>
+        <x:v>6.3121387283236992</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HAC</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>6.3135313531353132</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -9699,6 +9763,22 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>HCM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>16.012820512820515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>HEM</x:t>
         </x:is>
       </x:c>
@@ -11165,7 +11245,23 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>14.870129870129871</x:v>
+        <x:v>14.774193548387096</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HEM</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>11.397959183673469</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -12637,7 +12733,23 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>7.5348837209302326</x:v>
+        <x:v>7.5101449275362322</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HIJPII</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>7.7639751552795033</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14045,7 +14157,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>8.864890580399619</x:v>
+        <x:v>8.8733333333333331</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14077,7 +14189,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>8.5760667903525043</x:v>
+        <x:v>8.6080074487895715</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14093,7 +14205,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>8.4624781849912747</x:v>
+        <x:v>8.4698689956331883</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -14109,7 +14221,23 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>8.935574229691877</x:v>
+        <x:v>8.94392523364486</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>HJK</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>9.0463137996219274</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -15587,6 +15715,22 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>HJXXIII</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>7.5608732157850547</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>HMAL</x:t>
         </x:is>
       </x:c>
@@ -17059,6 +17203,22 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>HMAL</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>HRAD</x:t>
         </x:is>
       </x:c>
@@ -18531,6 +18691,22 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>HRAD</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>5.4491525423728815</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>HRBJA</x:t>
         </x:is>
       </x:c>
@@ -20003,6 +20179,22 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>HRBJA</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>7.83445945945946</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>HRJP</x:t>
         </x:is>
       </x:c>
@@ -21475,6 +21667,22 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>HRJP</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>7.30787037037037</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>IRS</x:t>
         </x:is>
       </x:c>
@@ -22947,6 +23155,22 @@
     <x:row>
       <x:c t="inlineStr">
         <x:is>
+          <x:t>IRS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>28.911392405063292</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
           <x:t>MOV</x:t>
         </x:is>
       </x:c>
@@ -23949,7 +24173,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>4.7194928684627575</x:v>
+        <x:v>4.712025316455696</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -23981,7 +24205,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>4.3301127214170689</x:v>
+        <x:v>4.323151125401929</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24029,7 +24253,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>4.693121693121693</x:v>
+        <x:v>4.6848591549295771</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24285,7 +24509,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>5.9712643678160919</x:v>
+        <x:v>5.9598470363288722</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24333,7 +24557,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c s="9">
-        <x:v>5.3795275590551181</x:v>
+        <x:v>5.38801261829653</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -24414,6 +24638,22 @@
       </x:c>
       <x:c s="9">
         <x:v>4.6872964169381106</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>MOV</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c s="8">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>4.4733096085409256</x:v>
       </x:c>
     </x:row>
     <x:row/>
